--- a/422-contenu-fhir---mise-à-jour-du-séjour/ig/CodeSystem-tddui-discriminator-cs.xlsx
+++ b/422-contenu-fhir---mise-à-jour-du-séjour/ig/CodeSystem-tddui-discriminator-cs.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-29T15:49:35+00:00</t>
+    <t>2026-01-30T11:01:37+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/422-contenu-fhir---mise-à-jour-du-séjour/ig/CodeSystem-tddui-discriminator-cs.xlsx
+++ b/422-contenu-fhir---mise-à-jour-du-séjour/ig/CodeSystem-tddui-discriminator-cs.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-30T11:01:37+00:00</t>
+    <t>2026-01-30T14:32:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
